--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104569_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104569_W13.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9529</v>
+        <v>4.7891</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9457</v>
+        <v>5.4059</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9928</v>
+        <v>-0.6167</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7119</v>
+        <v>3.7058</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0491</v>
+        <v>-0.0461</v>
       </c>
       <c r="I2" t="n">
-        <v>3.761</v>
+        <v>3.7519</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8599</v>
+        <v>4.837</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2353</v>
+        <v>0.2273</v>
       </c>
       <c r="L2" t="n">
-        <v>4.6246</v>
+        <v>4.6097</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.148</v>
+        <v>-1.1312</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1581</v>
+        <v>0.986</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0858</v>
+        <v>0.5688</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0723</v>
+        <v>0.4171</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5884</v>
+        <v>4.7403</v>
       </c>
       <c r="E3" t="n">
-        <v>4.093</v>
+        <v>3.2255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4954</v>
+        <v>1.5148</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8448</v>
+        <v>3.0807</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9337</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9112</v>
+        <v>2.4653</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6707</v>
+        <v>4.3987</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1704</v>
+        <v>1.2336</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5002</v>
+        <v>3.1651</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8258</v>
+        <v>-1.318</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2368</v>
+        <v>-0.6182</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5891</v>
+        <v>-0.6998</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>0.995</v>
+        <v>0.5214</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6472</v>
+        <v>-0.0351</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3478</v>
+        <v>0.5565</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8701</v>
+        <v>4.2307</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6023</v>
+        <v>3.7187</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2679</v>
+        <v>0.512</v>
       </c>
       <c r="G4" t="n">
-        <v>3.095</v>
+        <v>2.8361</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6294</v>
+        <v>0.928</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4656</v>
+        <v>1.9081</v>
       </c>
       <c r="J4" t="n">
-        <v>4.432</v>
+        <v>3.653</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2601</v>
+        <v>1.1581</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1719</v>
+        <v>2.4949</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3371</v>
+        <v>-0.8169</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6308</v>
+        <v>-0.2301</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7063</v>
+        <v>-0.5868</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.359</v>
+        <v>0.6434</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6956</v>
+        <v>0.2949</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3366</v>
+        <v>0.3485</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3803</v>
+        <v>2.8686</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8934</v>
+        <v>3.2343</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.513</v>
+        <v>-0.3657</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0519</v>
+        <v>2.058</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4937</v>
+        <v>-0.4831</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5455</v>
+        <v>2.5411</v>
       </c>
       <c r="J5" t="n">
-        <v>3.589</v>
+        <v>3.576</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4678</v>
+        <v>3.4554</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5371</v>
+        <v>-1.518</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5789</v>
+        <v>-0.0999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1167</v>
+        <v>0.2418</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8195</v>
+        <v>1.7034</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5551</v>
+        <v>4.2078</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2643</v>
+        <v>-2.5043</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8991</v>
+        <v>2.1052</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.7761</v>
+        <v>-0.2613</v>
       </c>
       <c r="I6" t="n">
-        <v>0.877</v>
+        <v>2.3665</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1779</v>
+        <v>3.8653</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.193</v>
+        <v>0.3135</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0151</v>
+        <v>3.5517</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7212</v>
+        <v>-1.7601</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1381</v>
+        <v>-1.1852</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3576</v>
+        <v>0.1917</v>
       </c>
       <c r="T6" t="n">
-        <v>1.733</v>
+        <v>-0.1535</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.3452</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5228</v>
+        <v>1.4204</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7054</v>
+        <v>1.4053</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1826</v>
+        <v>0.0151</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1164</v>
+        <v>0.6224</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2612</v>
+        <v>-0.9415</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3776</v>
+        <v>1.5639</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8962</v>
+        <v>1.5668</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3219</v>
+        <v>-0.697</v>
       </c>
       <c r="L7" t="n">
-        <v>3.5743</v>
+        <v>2.2638</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7798</v>
+        <v>-0.9444</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5831</v>
+        <v>-0.2446</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1967</v>
+        <v>-0.6998</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0058</v>
+        <v>0.7085</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6956</v>
+        <v>0.4319</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6899</v>
+        <v>0.2766</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>1.639</v>
+        <v>0.5447</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9378</v>
+        <v>1.3969</v>
       </c>
       <c r="E8" t="n">
-        <v>1.185</v>
+        <v>1.5852</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2472</v>
+        <v>-0.1883</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5544</v>
+        <v>0.5523</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0663</v>
+        <v>1.071</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5118</v>
+        <v>-0.5187</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9501</v>
+        <v>1.9269</v>
       </c>
       <c r="K8" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2531</v>
+        <v>0.2377</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3957</v>
+        <v>-1.3745</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3632</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>-0.3417</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4019</v>
+        <v>0.4335</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6499</v>
+        <v>0.676</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5891</v>
+        <v>0.5455</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0609</v>
+        <v>0.1305</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6353</v>
+        <v>-1.9033</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-2.7854</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5673</v>
+        <v>0.8821</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5943</v>
+        <v>-0.1998</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6793</v>
+        <v>-2.2105</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2736</v>
+        <v>2.0108</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.959</v>
+        <v>-1.7036</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2526</v>
+        <v>-0.5749</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7063</v>
+        <v>-1.1287</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.078</v>
+        <v>1.2136</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4174</v>
+        <v>0.7453</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3393</v>
+        <v>0.4683</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4947</v>
+        <v>0.2902</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3382</v>
+        <v>1.9863</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8435</v>
+        <v>-1.696</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1781</v>
+        <v>-0.1809</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7361</v>
+        <v>0.7244</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9142</v>
+        <v>-0.9053</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3699</v>
+        <v>1.3503</v>
       </c>
       <c r="K10" t="n">
-        <v>1.146</v>
+        <v>1.1269</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.548</v>
+        <v>-1.5312</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9243</v>
+        <v>0.7199</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8075</v>
+        <v>0.4782</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1167</v>
+        <v>0.2418</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>N. DJEDOVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2339</v>
+        <v>0.1891</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7611</v>
+        <v>0.3325</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5272</v>
+        <v>-0.1435</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7186</v>
+        <v>-0.6123</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7821</v>
+        <v>-1.3929</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5007</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4616</v>
+        <v>0.5626</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2149</v>
+        <v>-0.7035</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6765</v>
+        <v>1.2661</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7431</v>
+        <v>-1.1749</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5672</v>
+        <v>-0.6895</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1759</v>
+        <v>-0.4854</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.1184</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2994</v>
+        <v>-0.2301</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5619</v>
+        <v>0.3485</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. DJEDOVIC</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0664</v>
+        <v>-0.4801</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2212</v>
+        <v>1.2751</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1548</v>
+        <v>-1.7552</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6141</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3924</v>
+        <v>-0.7813</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7784</v>
+        <v>1.4985</v>
       </c>
       <c r="J12" t="n">
-        <v>0.569</v>
+        <v>1.4472</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6998</v>
+        <v>-0.2208</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2688</v>
+        <v>1.668</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1831</v>
+        <v>-0.73</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6927</v>
+        <v>-0.5604</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4904</v>
+        <v>-0.1695</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0</v>
+        <v>0.1394</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3478</v>
+        <v>-0.1721</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3478</v>
+        <v>0.3115</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.5432</v>
+        <v>-1.1621</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7532</v>
+        <v>1.1441</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2964</v>
+        <v>-2.3062</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.9626</v>
+        <v>-1.9625</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.1039</v>
+        <v>-2.1024</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1413</v>
+        <v>0.14</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5748</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.5208</v>
+        <v>-1.5276</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9648</v>
+        <v>0.9528</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4066</v>
+        <v>-1.3877</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6318</v>
+        <v>-0.2404</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8347</v>
+        <v>-0.4114</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2029</v>
+        <v>0.171</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W13" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.9735</v>
+        <v>20.6625</v>
       </c>
       <c r="E14" t="n">
-        <v>27.6427</v>
+        <v>28.06619999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.669</v>
+        <v>-7.403499999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>11.0744</v>
+        <v>11.0187</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.425000000000001</v>
+        <v>-5.4552</v>
       </c>
       <c r="I14" t="n">
-        <v>16.4996</v>
+        <v>16.4741</v>
       </c>
       <c r="J14" t="n">
-        <v>26.6589</v>
+        <v>26.4092</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6441000000000003</v>
+        <v>0.5099</v>
       </c>
       <c r="L14" t="n">
-        <v>26.0146</v>
+        <v>25.8994</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.5845</v>
+        <v>-15.3905</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.0694</v>
+        <v>-5.965299999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.5152</v>
+        <v>-9.4252</v>
       </c>
       <c r="P14" t="n">
-        <v>6.8049</v>
+        <v>6.828900000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.5368</v>
+        <v>-4.5528</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S14" t="n">
-        <v>4.279699999999999</v>
+        <v>4.9938</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1210000000000001</v>
+        <v>0.8334999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>4.1583</v>
+        <v>4.1603</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.1854</v>
+        <v>-2.1791</v>
       </c>
       <c r="W14" t="n">
-        <v>5.3991</v>
+        <v>5.3759</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.584499999999999</v>
+        <v>-7.555</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8568</v>
+        <v>0.7661</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9683</v>
+        <v>3.1627</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1115</v>
+        <v>-2.3966</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2115</v>
+        <v>-0.2105</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8009</v>
+        <v>1.7926</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.0124</v>
+        <v>-2.0031</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7465</v>
+        <v>2.7232</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4404</v>
+        <v>1.4199</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.9579</v>
+        <v>-2.9337</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.3185</v>
+        <v>-3.3064</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0151</v>
+        <v>-0.0626</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7652</v>
+        <v>-0.5298</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7803</v>
+        <v>0.4672</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1212</v>
+        <v>2.1075</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1265</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6178</v>
+        <v>4.0444</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.7443</v>
+        <v>-3.4552</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2944</v>
+        <v>2.2907</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5583</v>
+        <v>2.559</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2639</v>
+        <v>-0.2683</v>
       </c>
       <c r="J16" t="n">
-        <v>5.7954</v>
+        <v>5.7543</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7809</v>
+        <v>2.7612</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0145</v>
+        <v>2.9932</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.501</v>
+        <v>-3.4637</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2225</v>
+        <v>-0.2022</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.2785</v>
+        <v>-3.2615</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6477</v>
+        <v>-0.929</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0434</v>
+        <v>-0.5718</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.3573</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1092</v>
+        <v>-1.0191</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1069</v>
+        <v>2.1428</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.2161</v>
+        <v>-3.1619</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7019</v>
+        <v>0.4336</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9854000000000001</v>
+        <v>2.7486</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7166</v>
+        <v>-2.315</v>
       </c>
       <c r="J17" t="n">
-        <v>5.0758</v>
+        <v>4.2567</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1602</v>
+        <v>3.0509</v>
       </c>
       <c r="L17" t="n">
-        <v>3.9156</v>
+        <v>1.2058</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3738</v>
+        <v>-3.8232</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1749</v>
+        <v>-0.3023</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.199</v>
+        <v>-3.5209</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7431</v>
+        <v>-0.5634</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2994</v>
+        <v>-0.9271</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0425</v>
+        <v>0.3637</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2534</v>
+        <v>0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1509</v>
+        <v>-1.0556</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9231</v>
+        <v>-0.927</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2278</v>
+        <v>-0.1286</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0048</v>
+        <v>-1.0033</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3333</v>
+        <v>0.3359</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3381</v>
+        <v>-1.3392</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7144</v>
+        <v>-0.7179</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2904</v>
+        <v>-0.2854</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1461</v>
+        <v>-0.0523</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0626</v>
+        <v>0.1568</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2812</v>
+        <v>-1.1223</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0693</v>
+        <v>2.8456</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3505</v>
+        <v>-3.9679</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4378</v>
+        <v>2.7089</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7488</v>
+        <v>0.996</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.311</v>
+        <v>1.7129</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2884</v>
+        <v>5.0571</v>
       </c>
       <c r="K19" t="n">
-        <v>3.0651</v>
+        <v>1.1549</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2233</v>
+        <v>3.9022</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.8506</v>
+        <v>-2.3481</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3162</v>
+        <v>-0.1588</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.5344</v>
+        <v>-2.1893</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8363</v>
+        <v>-0.763</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0434</v>
+        <v>0.0648</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2072</v>
+        <v>-0.8278</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9320000000000001</v>
+        <v>-1.2472</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7628</v>
+        <v>-1.3798</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0426</v>
+        <v>2.1464</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8054</v>
+        <v>-3.5262</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.971</v>
+        <v>-0.9547</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1314</v>
+        <v>-0.1239</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8396</v>
+        <v>-0.8308</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6456</v>
+        <v>1.6355</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1456</v>
+        <v>-0.1519</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6166</v>
+        <v>-2.5902</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.6308</v>
+        <v>-2.6182</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2455</v>
+        <v>-0.8803</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6956</v>
+        <v>-0.5786</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5498</v>
+        <v>-0.3017</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1674</v>
+        <v>-1.8372</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2594</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4268</v>
+        <v>-2.4365</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.1564</v>
+        <v>-4.1428</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2382</v>
+        <v>-0.2329</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.9183</v>
+        <v>-3.9099</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2303</v>
+        <v>-1.238</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-0.6345</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9261</v>
+        <v>-2.9048</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3923</v>
+        <v>0.4016</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.3185</v>
+        <v>-3.3064</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4231</v>
+        <v>-0.101</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2725</v>
+        <v>0.2407</v>
       </c>
       <c r="V21" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2259</v>
+        <v>-2.1301</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.164</v>
+        <v>-1.1686</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0619</v>
+        <v>-0.9615</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8579</v>
+        <v>-0.8515</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3435</v>
+        <v>-0.3391</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5144</v>
+        <v>-0.5123</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1093</v>
+        <v>0.1089</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.9604</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2338</v>
+        <v>-0.1405</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.349</v>
+        <v>-2.8476</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5407</v>
+        <v>1.2837</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8897</v>
+        <v>-4.1313</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9264</v>
+        <v>-0.907</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1156</v>
+        <v>-1.1008</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1893</v>
+        <v>0.1939</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7697</v>
+        <v>1.7555</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5786</v>
+        <v>-0.5828</v>
       </c>
       <c r="L23" t="n">
-        <v>2.3482</v>
+        <v>2.3383</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.696</v>
+        <v>-2.6624</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5371</v>
+        <v>-0.518</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.159</v>
+        <v>-2.1444</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1031</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1875</v>
+        <v>-0.4231</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0844</v>
+        <v>-0.2005</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1302</v>
+        <v>-4.2353</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7796</v>
+        <v>-2.6889</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3506</v>
+        <v>-1.5464</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8469</v>
+        <v>-2.8453</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5222</v>
+        <v>-1.5304</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3247</v>
+        <v>-1.3149</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0194</v>
+        <v>-1.0419</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.206</v>
+        <v>-1.228</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8275</v>
+        <v>-1.8034</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6028</v>
+        <v>-0.7071</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6261</v>
+        <v>-0.5089</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0233</v>
+        <v>-0.1983</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5274</v>
+        <v>-5.6937</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0695</v>
+        <v>-4.0367</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4579</v>
+        <v>-1.6569</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.5337</v>
+        <v>-5.5368</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3492</v>
+        <v>0.3503</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.8829</v>
+        <v>-5.8872</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.8821</v>
+        <v>-2.9029</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.9962</v>
+        <v>-3.0096</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.6516</v>
+        <v>-2.6339</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.8867</v>
+        <v>-2.8775</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>1.6867</v>
+        <v>0.5261</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9467</v>
+        <v>0.0044</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7401</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-19.9737</v>
+        <v>-19.9654</v>
       </c>
       <c r="E26" t="n">
-        <v>7.668799999999999</v>
+        <v>7.403700000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-27.6425</v>
+        <v>-27.369</v>
       </c>
       <c r="G26" t="n">
-        <v>-11.0745</v>
+        <v>-11.0187</v>
       </c>
       <c r="H26" t="n">
-        <v>5.425</v>
+        <v>5.4553</v>
       </c>
       <c r="I26" t="n">
-        <v>-16.4994</v>
+        <v>-16.4739</v>
       </c>
       <c r="J26" t="n">
-        <v>15.5845</v>
+        <v>15.3905</v>
       </c>
       <c r="K26" t="n">
-        <v>6.069199999999999</v>
+        <v>5.965400000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>9.5151</v>
+        <v>9.4254</v>
       </c>
       <c r="M26" t="n">
-        <v>-26.6587</v>
+        <v>-26.4092</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.6443000000000002</v>
+        <v>-0.5098</v>
       </c>
       <c r="O26" t="n">
-        <v>-26.0149</v>
+        <v>-25.8993</v>
       </c>
       <c r="P26" t="n">
-        <v>-6.805000000000001</v>
+        <v>-6.829</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.3418</v>
+        <v>-11.3818</v>
       </c>
       <c r="R26" t="n">
-        <v>4.5367</v>
+        <v>4.5527</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.279700000000001</v>
+        <v>-4.2966</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.158500000000001</v>
+        <v>-4.160299999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1208999999999999</v>
+        <v>-0.1365999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W26" t="n">
-        <v>7.584599999999999</v>
+        <v>7.5549</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.3991</v>
+        <v>-5.3759</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104569_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104569_W13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.555</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104569_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-5.3759</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
